--- a/pla_solu.xlsx
+++ b/pla_solu.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Scripts_SQL\ScriptsSQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDB690F0-C71F-4CBA-917F-F38C8D3C818D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE752B6B-5483-4ECC-8203-6650EF9FDAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{922F879F-3E4A-43B5-BF4C-DE7768608FAF}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{922F879F-3E4A-43B5-BF4C-DE7768608FAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="354">
   <si>
     <t>Edi_Pra int,</t>
   </si>
@@ -1082,6 +1083,21 @@
   </si>
   <si>
     <t>SELECT TOP 1 * FROM PCXVE</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>(</t>
+  </si>
+  <si>
+    <t>)</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1121,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,12 +1136,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1161,16 +1183,179 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1178,14 +1363,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1500,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E75EFA-3D73-4A88-821D-E5AF2F22CF24}">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -1511,41 +1753,41 @@
     <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="24"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1565,7 +1807,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1585,7 +1827,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1604,9 +1846,8 @@
       <c r="F5" t="s">
         <v>210</v>
       </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1626,7 +1867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1646,7 +1887,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1666,7 +1907,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1686,7 +1927,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1706,7 +1947,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1726,7 +1967,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1746,7 +1987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -1766,7 +2007,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1786,7 +2027,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1806,7 +2047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2889,12 +3130,12 @@
     <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -2940,1200 +3181,1618 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="U2" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Y2" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="Z2" s="5" t="s">
+      <c r="Z2" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="AA2" s="5" t="s">
+      <c r="AA2" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AB2" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AC2" s="5" t="s">
+      <c r="AC2" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AD2" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AF2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AG2" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AH2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AI2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AK2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="AL2" s="5" t="s">
+      <c r="AL2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="AM2" s="5" t="s">
+      <c r="AM2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AN2" s="5" t="s">
+      <c r="AN2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="AO2" s="5" t="s">
+      <c r="AO2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="AP2" s="5" t="s">
+      <c r="AP2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AQ2" s="5" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AR2" s="5" t="s">
+      <c r="AR2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AS2" s="5" t="s">
+      <c r="AS2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="AT2" s="5" t="s">
+      <c r="AT2" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="AU2" s="5" t="s">
+      <c r="AU2" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="AV2" s="5" t="s">
+      <c r="AV2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="AW2" s="5" t="s">
+      <c r="AW2" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="AX2" s="5" t="s">
+      <c r="AX2" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="AY2" s="5" t="s">
+      <c r="AY2" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="AZ2" s="5" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="BA2" s="5" t="s">
+      <c r="BA2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="BB2" s="5" t="s">
+      <c r="BB2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="BC2" s="5" t="s">
+      <c r="BC2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="BD2" s="5" t="s">
+      <c r="BD2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="BE2" s="5" t="s">
+      <c r="BE2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="BF2" s="5" t="s">
+      <c r="BF2" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="BG2" s="5" t="s">
+      <c r="BG2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="BH2" s="5" t="s">
+      <c r="BH2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="BI2" s="5" t="s">
+      <c r="BI2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="BJ2" s="5" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="23">
         <v>40694</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="23">
         <v>40695</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="7">
         <v>0</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="7">
         <v>1</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="8">
         <v>2500000</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="3">
         <v>60</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="4">
         <v>44697.03125</v>
       </c>
-      <c r="R3" s="5">
+      <c r="R3" s="3">
         <v>0</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="3">
         <v>0</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T3" s="3">
         <v>0</v>
       </c>
-      <c r="U3" s="5">
+      <c r="U3" s="3">
         <v>0</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="3">
         <v>1</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="Z3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AA3" s="5">
+      <c r="AA3" s="3">
         <v>0</v>
       </c>
-      <c r="AB3" s="5">
+      <c r="AB3" s="3">
         <v>0</v>
       </c>
-      <c r="AC3" s="5">
+      <c r="AC3" s="3">
         <v>0</v>
       </c>
-      <c r="AD3" s="5">
+      <c r="AD3" s="3">
         <v>0</v>
       </c>
-      <c r="AE3" s="5">
+      <c r="AE3" s="3">
         <v>0</v>
       </c>
-      <c r="AF3" s="5">
+      <c r="AF3" s="3">
         <v>0</v>
       </c>
-      <c r="AG3" s="6">
+      <c r="AG3" s="4">
         <v>40465</v>
       </c>
-      <c r="AH3" s="5" t="s">
+      <c r="AH3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="AI3" s="5" t="s">
+      <c r="AI3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="AJ3" s="5">
+      <c r="AJ3" s="3">
         <v>0</v>
       </c>
-      <c r="AK3" s="5" t="s">
+      <c r="AK3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AL3" s="5">
+      <c r="AL3" s="3">
         <v>1</v>
       </c>
-      <c r="AM3" s="5">
+      <c r="AM3" s="3">
         <v>0</v>
       </c>
-      <c r="AN3" s="5">
+      <c r="AN3" s="3">
         <v>0</v>
       </c>
-      <c r="AO3" s="5">
+      <c r="AO3" s="3">
         <v>0</v>
       </c>
-      <c r="AP3" s="5" t="s">
+      <c r="AP3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="AQ3" s="5" t="s">
+      <c r="AQ3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AR3" s="5" t="s">
+      <c r="AR3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AS3" s="5">
+      <c r="AS3" s="3">
         <v>0</v>
       </c>
-      <c r="AT3" s="5"/>
-      <c r="AU3" s="5">
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="3">
         <v>0</v>
       </c>
-      <c r="AV3" s="5">
+      <c r="AV3" s="3">
         <v>0</v>
       </c>
-      <c r="AW3" s="5" t="s">
+      <c r="AW3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="AX3" s="5">
+      <c r="AX3" s="3">
         <v>0</v>
       </c>
-      <c r="AY3" s="5" t="s">
+      <c r="AY3" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="AZ3" s="5">
+      <c r="AZ3" s="3">
         <v>0</v>
       </c>
-      <c r="BA3" s="5">
+      <c r="BA3" s="3">
         <v>0</v>
       </c>
-      <c r="BB3" s="5">
+      <c r="BB3" s="3">
         <v>0</v>
       </c>
-      <c r="BC3" s="5">
+      <c r="BC3" s="3">
         <v>0</v>
       </c>
-      <c r="BD3" s="5" t="s">
+      <c r="BD3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BE3" s="5" t="s">
+      <c r="BE3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BF3" s="5" t="s">
+      <c r="BF3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BG3" s="5" t="s">
+      <c r="BG3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BH3" s="5" t="s">
+      <c r="BH3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BI3" s="5">
+      <c r="BI3" s="3">
         <v>0</v>
       </c>
-      <c r="BJ3" s="5" t="s">
+      <c r="BJ3" s="3" t="s">
         <v>230</v>
       </c>
     </row>
+    <row r="4" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="I5" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="38"/>
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="I6" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="7" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>0</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="I7" s="16">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I8" s="18"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="19"/>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I9" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="31"/>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I10" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I11" s="16">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="34"/>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="I14" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="J14" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="L14" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="M14" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="I14" s="5" t="s">
+      <c r="N14" s="11"/>
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I15" s="10">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11">
+        <v>60</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="I16" s="18"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="I17" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="28"/>
+    </row>
+    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="I18" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="K14" s="5" t="s">
+      <c r="J18" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L18" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M18" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="N18" s="7"/>
+      <c r="O18" s="17"/>
+    </row>
+    <row r="19" spans="8:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="20">
         <v>1</v>
       </c>
-      <c r="B15" s="5">
+      <c r="J19" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="K19" s="21">
+        <v>0</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="N19" s="21"/>
+      <c r="O19" s="22"/>
+    </row>
+    <row r="22" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H22" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+    </row>
+    <row r="23" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H23" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q23" s="6"/>
+    </row>
+    <row r="24" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H24" s="7">
         <v>1</v>
       </c>
-      <c r="C15" s="5">
+      <c r="I24" s="7">
+        <v>2</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q24" s="6"/>
+    </row>
+    <row r="25" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+    </row>
+    <row r="26" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H26" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+    </row>
+    <row r="27" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H28" s="7">
+        <v>1</v>
+      </c>
+      <c r="I28" s="7">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q28" s="7">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="s">
+    </row>
+    <row r="29" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+    </row>
+    <row r="30" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H30" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+    </row>
+    <row r="31" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q31" s="9"/>
+    </row>
+    <row r="32" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H32" s="7">
+        <v>1</v>
+      </c>
+      <c r="I32" s="7">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="K32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="L32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="M32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="N32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="O32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="P32" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="Q32" s="6"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>2</v>
+      </c>
+      <c r="B47" s="7">
+        <v>1</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A49" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="U50" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="V50" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="W50" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="X50" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y50" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z50" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA50" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB50" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="AC50" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="AD50" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>1</v>
+      </c>
+      <c r="B51" s="7">
+        <v>564</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7">
+        <v>60</v>
+      </c>
+      <c r="E51" s="8">
+        <v>98600</v>
+      </c>
+      <c r="F51" s="8">
+        <v>98600</v>
+      </c>
+      <c r="G51" s="7">
+        <v>3</v>
+      </c>
+      <c r="H51" s="5">
+        <v>180800</v>
+      </c>
+      <c r="I51" s="3">
+        <v>6</v>
+      </c>
+      <c r="J51" s="5">
+        <v>235600</v>
+      </c>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="O51" s="5">
+        <v>365000000</v>
+      </c>
+      <c r="P51" s="5">
+        <v>180800</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>235600</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="AA51" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="I15" s="5">
+      <c r="AB51" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC51" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD51" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A53" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>764</v>
+      </c>
+      <c r="B55" s="7">
+        <v>10999</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="7"/>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A57" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>3</v>
+      </c>
+      <c r="B59" s="7">
         <v>1</v>
       </c>
-      <c r="J15" s="5">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
-        <v>60</v>
-      </c>
-      <c r="L15" s="5" t="s">
+      <c r="C59" s="7">
+        <v>90</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="E59" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>1</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H22" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H23" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H24" s="5">
-        <v>1</v>
-      </c>
-      <c r="I24" s="5">
-        <v>2</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H26" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H27" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H28" s="5">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5">
-        <v>1</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="P28" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H30" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H31" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q31" s="4"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H32" s="5">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="K32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="L32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="M32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="N32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="O32" s="7">
-        <v>1000000</v>
-      </c>
-      <c r="P32" s="7">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
-        <v>2</v>
-      </c>
-      <c r="B39" s="5">
-        <v>1</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>1</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C43" s="5">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="N50" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="O50" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="P50" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q50" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="R50" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="S50" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="T50" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="U50" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="V50" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="W50" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="X50" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="Y50" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="Z50" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA50" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB50" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AC50" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD50" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
-        <v>1</v>
-      </c>
-      <c r="B51" s="5">
-        <v>564</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5">
-        <v>60</v>
-      </c>
-      <c r="E51" s="7">
-        <v>98600</v>
-      </c>
-      <c r="F51" s="7">
-        <v>98600</v>
-      </c>
-      <c r="G51" s="5">
-        <v>3</v>
-      </c>
-      <c r="H51" s="7">
-        <v>180800</v>
-      </c>
-      <c r="I51" s="5">
-        <v>6</v>
-      </c>
-      <c r="J51" s="7">
-        <v>235600</v>
-      </c>
-      <c r="K51" s="5">
-        <v>0</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="M51" s="5">
-        <v>0</v>
-      </c>
-      <c r="N51" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="O51" s="7">
-        <v>365000000</v>
-      </c>
-      <c r="P51" s="7">
-        <v>180800</v>
-      </c>
-      <c r="Q51" s="7">
-        <v>235600</v>
-      </c>
-      <c r="R51" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="S51" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="T51" s="5">
-        <v>0</v>
-      </c>
-      <c r="U51" s="5">
-        <v>0</v>
-      </c>
-      <c r="V51" s="5">
-        <v>0</v>
-      </c>
-      <c r="W51" s="5">
-        <v>0</v>
-      </c>
-      <c r="X51" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="5"/>
-      <c r="Z51" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA51" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB51" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC51" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="AD51" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
-        <v>764</v>
-      </c>
-      <c r="B55" s="5">
-        <v>10999</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="5">
-        <v>0</v>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
-        <v>3</v>
-      </c>
-      <c r="B59" s="5">
-        <v>1</v>
-      </c>
-      <c r="C59" s="5">
-        <v>90</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="I17:O17"/>
     <mergeCell ref="H26:N26"/>
     <mergeCell ref="H30:N30"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="I9:O9"/>
     <mergeCell ref="H22:N22"/>
+    <mergeCell ref="I13:O13"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="I13:O13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44B7ADA-12BF-471A-922A-B85B9924DED5}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="1.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>351</v>
+      </c>
+      <c r="B9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>351</v>
+      </c>
+      <c r="B18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>351</v>
+      </c>
+      <c r="B20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>351</v>
+      </c>
+      <c r="B22" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B24" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>351</v>
+      </c>
+      <c r="B25" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" t="s">
+        <v>350</v>
+      </c>
+      <c r="D25" t="s">
+        <v>352</v>
+      </c>
+      <c r="E25">
+        <v>0.01</v>
+      </c>
+      <c r="F25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>351</v>
+      </c>
+      <c r="B26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>351</v>
+      </c>
+      <c r="B27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" t="s">
+        <v>267</v>
+      </c>
+      <c r="C29" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" t="s">
+        <v>268</v>
+      </c>
+      <c r="C30" t="s">
+        <v>349</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>